--- a/questionnaire_templates/031_squamous_cell_carcinoma_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/031_squamous_cell_carcinoma_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,20 +525,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of Squamous Cell Carcinoma.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,20 +552,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_squamous_cell_carcinoma</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What are the risk factors for Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_is_squamous_cell_carcinoma</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the primary site of Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide a brief description.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_are_the_risk_factors</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What are the most common symptoms of Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_are_the_risk_factors</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What are the treatment options for Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide a brief description.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,79 +660,95 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_is_the_primary_site_of_squamous_cell_carcinoma</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the prognosis for Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_3_answer</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_is_the_primary_site_of_squamous_cell_carcinoma</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What are the common complications of Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_is_the_most_common_symptom</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide a brief conclusion.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_4_answer</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_is_the_most_common_symptom</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional comments?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Any additional comments or concerns about Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>what_are_the_treatment_options</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Any relevant references or studies related to Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_5_answer</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what_are_the_treatment_options</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Additional Resources</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Any recommended resources or links related to Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what_are_the_risk_factors_for_squamous_cell_carcinoma</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Is there anything else you would like to share about Squamous Cell Carcinoma?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,41 +844,49 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_6_answer</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>what_are_the_risk_factors_for_squamous_cell_carcinoma</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Confirmation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please confirm that you have read and understood the information provided.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>what_is_the_prognosis</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Agreement</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide your agreement to the information provided.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,41 +898,49 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_7_answer</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>what_is_the_prognosis</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide your certification of understanding.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>what_are_the_common_complications</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Disclaimer</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please provide your disclaimer of understanding.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,41 +952,49 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_8_answer</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>what_are_the_common_complications</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Acknowledgement</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide your acknowledgement of understanding.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>conclusion</t>
+          <t>question_15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>conclusion</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Acknowledgement of Understanding</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please confirm that you have read, understood, and agreed to all the information provided.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -937,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -965,51 +1037,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_answer_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>family_history</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Family History</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_answer_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>smoking</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Smoking</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>previous_history_with_cancer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Previous History with Cancer</t>
         </is>
       </c>
     </row>
@@ -1021,216 +1093,148 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hoarseness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hoarseness</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weight Loss</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>respiratory_failure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Respiratory Failure</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neurological_damage</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neurological Damage</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cardiovascular_issues</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Cardiovascular Issues</t>
         </is>
       </c>
     </row>
